--- a/public/templates/process-docs/定位放线工程检验批质量验收记录.xlsx
+++ b/public/templates/process-docs/定位放线工程检验批质量验收记录.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-SG-ZHHC-03-01-01-01-001</t>
+    <t xml:space="preserve">{{文件编号}}</t>
   </si>
   <si>
     <t xml:space="preserve">单位（子单位）
@@ -172,13 +172,13 @@
     <t xml:space="preserve">施工单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目经理</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工执行标
@@ -211,19 +211,19 @@
 （施工员）</t>
   </si>
   <si>
-    <t xml:space="preserve">刘彦堂</t>
+    <t xml:space="preserve">{{施工单位项目技术负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包项目经理</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工班组长</t>
@@ -469,7 +469,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">河南中核五院研究设计有限公司</t>
+    <t xml:space="preserve">{{监理项目部}}</t>
   </si>
 </sst>
 </file>
